--- a/rsvp_forms/008_exclusive_preview_patron_rsvp--rsvp_forms.xlsx
+++ b/rsvp_forms/008_exclusive_preview_patron_rsvp--rsvp_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'wheelchair_accessible'}</t>
+          <t>wheelchair_accessible</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Wheelchair Accessible'}</t>
+          <t>Wheelchair Accessible</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'wheelchair_accessible_(wheelchair_and_companion)'}</t>
+          <t>wheelchair_accessible_(wheelchair_and_companion)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Wheelchair Accessible (Wheelchair and Companion)'}</t>
+          <t>Wheelchair Accessible (Wheelchair and Companion)</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'wheelchair_accessible_(service_animal)'}</t>
+          <t>wheelchair_accessible_(service_animal)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Wheelchair Accessible (Service Animal)'}</t>
+          <t>Wheelchair Accessible (Service Animal)</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'wheelchair_accessible_(service_animal_and_companion)'}</t>
+          <t>wheelchair_accessible_(service_animal_and_companion)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Wheelchair Accessible (Service Animal and Companion)'}</t>
+          <t>Wheelchair Accessible (Service Animal and Companion)</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'location_3'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Location 3'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'location_4'}</t>
+          <t>location_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Location 4'}</t>
+          <t>Location 4</t>
         </is>
       </c>
     </row>
